--- a/pesaje/analytica/Report/Recepcion-Export-Pesaje-Base.xlsx
+++ b/pesaje/analytica/Report/Recepcion-Export-Pesaje-Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB665A6-0CAC-474D-9749-99365909A5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91ADFCF-486E-4B39-A638-6E88D97535FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Analytica Mineral Services Sac</t>
   </si>
@@ -87,7 +87,10 @@
     <t>ESTADO PESAJE LIBRE</t>
   </si>
   <si>
-    <t>PLACA</t>
+    <t>PRODUCTO</t>
+  </si>
+  <si>
+    <t>ENVASE</t>
   </si>
 </sst>
 </file>
@@ -268,14 +271,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -561,23 +564,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="52.21875" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.88671875" style="4" customWidth="1"/>
     <col min="6" max="6" width="28.44140625" style="4" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" style="4" customWidth="1"/>
     <col min="8" max="8" width="28.5546875" style="4" customWidth="1"/>
     <col min="9" max="9" width="24.77734375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="4" customWidth="1"/>
-    <col min="11" max="18" width="24.6640625" style="4" customWidth="1"/>
+    <col min="10" max="11" width="14.88671875" style="4" customWidth="1"/>
+    <col min="12" max="19" width="24.6640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -596,7 +599,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
-      <c r="S1" s="1"/>
+      <c r="S1" s="5"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -618,29 +621,30 @@
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
     </row>
-    <row r="2" spans="1:40" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:41" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="5"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-      <c r="S2" s="1"/>
+      <c r="S2" s="5"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -662,29 +666,30 @@
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
       <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:40" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="5"/>
+      <c r="L3" s="7"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="1"/>
+      <c r="S3" s="5"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -706,8 +711,9 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -718,7 +724,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
+      <c r="K4" s="6"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -726,7 +732,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="1"/>
+      <c r="S4" s="5"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -748,8 +754,9 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
     </row>
-    <row r="5" spans="1:40" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -760,23 +767,24 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9"/>
     </row>
-    <row r="6" spans="1:40" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:40" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -788,8 +796,9 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:40" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -821,29 +830,32 @@
         <v>11</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>20</v>
+      <c r="R8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:40" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="F11" s="4" t="s">
         <v>7</v>
       </c>
